--- a/content/tz-obuchenie-v-kitae-dlya-russkih.xlsx
+++ b/content/tz-obuchenie-v-kitae-dlya-russkih.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Обучение в Китае для русских: четыре входа в вуз и что каждый стоит</t>
+          <t>Высшее образование в Китае для русских: четыре входа в вуз и что каждый стоит</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Обучение в Китае для русских начинается не с документов, а с выбора входа. Их четыре, и какой ваш — зависит от того, что уже есть на руках: аттестат с ЕГЭ, аттестат без ЕГЭ, диплом колледжа или диплом бакалавра. От входа зависят срок, язык обучения и цена. Разбираем все четыре, показываем, из чего складывается стоимость, и честно говорим, что бывает с дипломом после выпуска.</t>
+          <t>Высшее образование в Китае для русских начинается не с документов, а с выбора входа. Их четыре, и какой ваш — зависит от того, что уже есть на руках: аттестат с ЕГЭ, аттестат без ЕГЭ, диплом колледжа или диплом бакалавра. От входа зависят срок, язык обучения и цена. Разбираем все четыре, показываем, из чего складывается стоимость обучения в Китае, и честно говорим, что бывает с дипломом после выпуска.</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>38 424 знака (лимит ≈ 50 000)</t>
+          <t>38 519 знаков (лимит ≈ 50 000)</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>27,6 % (норма 26–31 %)</t>
+          <t>28,0 % (норма 26–31 %)</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>38,2 %; FAQ на 66,3 %</t>
+          <t>38,5 %; FAQ на 66,5 %</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Общий вход (3): обучение в китае для русских, учиться в китае, образование в китае для русских — тайтл, H1, паспорт, раздел 1. Вузы (5): высшее образование в китае, высшее образование в китае для россиян, китай вузы для русских, китай обучение в вузах для русских, обучение в университете китая для русских — раздел 1 и таблица четырёх входов. Цена (3): стоимость, цена, 2026 — раздел 2, честно через структуру расходов</t>
+          <t>Общий вход (3): обучение в китае для русских, учиться в китае, образование в китае для русских — паспорт, раздел 1, адрес страницы. Вузы (5): высшее образование в китае, высшее образование в китае для россиян, китай вузы для русских, китай обучение в вузах для русских, обучение в университете китая для русских — ТАЙТЛ, H1, ПАСПОРТ, раздел 1 и таблица четырёх входов. Цена (3): стоимость, цена, 2026 — раздел 2, честно через структуру расходов</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -939,41 +939,41 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>ТАЙТЛ «Чемодан, вокзал, Пекин»</t>
+          <t>ТАЙТЛ ПЕРЕПИСАН ВТОРОЙ РАЗ, уже после сдачи</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>ЗАМЕНЁН ЦЕЛИКОМ</t>
+          <t>Было «Обучение в Китае для русских…», стало «Высшее образование в Китае для русских…»</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>ПЕРВАЯ ПРИЧИНА НЕ ПРО SEO: «чемодан, вокзал, Пекин» — переделка лозунга «чемодан, вокзал, Россия», которым людей выгоняли по национальному признаку. На странице школы, которая зовёт русских учиться в Китае, такая отсылка читается скверно. ВТОРАЯ: тайтл не начинался с ключевой фразы и обещал документы и грант — то есть ровно то, что уже опубликовано двумя разделами</t>
+          <t>Заказчик прочитала начало как «обучение китайцам» — будто мы учим китайцев. В файлах такого текста не было: слово «китайц» — 0 вхождений в статье, блоке T123 и ТЗ. Но если фраза читается двояко у заказчика, она прочитается двояко и у части читателей. «Высшее образование в Китае» — тоже ключ из брифа, и спутать его не с чем. Ключ «обучение в Китае для русских» остался в теле статьи и в адресе страницы</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>«Пакет документов»</t>
+          <t>ТАЙТЛ «Чемодан, вокзал, Пекин»</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>СНЯТО, отдано ссылкой</t>
+          <t>ЗАМЕНЁН ЦЕЛИКОМ</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Целый раздел в Грантах</t>
+          <t>ПЕРВАЯ ПРИЧИНА НЕ ПРО SEO: «чемодан, вокзал, Пекин» — переделка лозунга «чемодан, вокзал, Россия», которым людей выгоняли по национальному признаку. На странице школы, которая зовёт русских учиться в Китае, такая отсылка читается скверно. ВТОРАЯ: тайтл не начинался с ключевой фразы и обещал документы и грант — то есть ровно то, что уже опубликовано двумя разделами</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>«Мотивационное письмо»</t>
+          <t>«Пакет документов»</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -983,14 +983,14 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Целый раздел в CSC, 15 упоминаний</t>
+          <t>Целый раздел в Грантах</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>«Что говорить на собеседовании»</t>
+          <t>«Мотивационное письмо»</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1000,90 +1000,107 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Целый раздел в CSC</t>
+          <t>Целый раздел в CSC, 15 упоминаний</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>«За счёт гранта»</t>
+          <t>«Что говорить на собеседовании»</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>СНЯТО ИЗ ЗАГОЛОВКА</t>
+          <t>СНЯТО, отдано ссылкой</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Гранты — один из способов оплаты, а не единственный путь. В статье даны строкой в разделе про цену и ссылками</t>
+          <t>Целый раздел в CSC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>«Без унылой теории раскладываем по полочкам»</t>
+          <t>«За счёт гранта»</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>СДЕЛАНО БУКВАЛЬНО</t>
+          <t>СНЯТО ИЗ ЗАГОЛОВКА</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Таблица четырёх входов: что нужно, куда ведёт, сколько длится</t>
+          <t>Гранты — один из способов оплаты, а не единственный путь. В статье даны строкой в разделе про цену и ссылками</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Добавлено сверх брифа</t>
+          <t>«Без унылой теории раскладываем по полочкам»</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Из чего складывается цена; что бывает с дипломом после выпуска</t>
+          <t>СДЕЛАНО БУКВАЛЬНО</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Иначе страница была бы пересказом четырёх своих же статей</t>
+          <t>Таблица четырёх входов: что нужно, куда ведёт, сколько длится</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ЦЕНА: три ключа</t>
+          <t>Добавлено сверх брифа</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ТОЧНЫХ СУММ НЕТ</t>
+          <t>Из чего складывается цена; что бывает с дипломом после выпуска</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Зависят от вуза, города, ступени и года, устаревают быстрее, чем публикуются. Даём структуру расходов. Это наша линия с Языковых курсов и Бесплатного образования</t>
+          <t>Иначе страница была бы пересказом четырёх своих же статей</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>ЦЕНА: три ключа</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>ТОЧНЫХ СУММ НЕТ</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Зависят от вуза, города, ступени и года, устаревают быстрее, чем публикуются. Даём структуру расходов. Это наша линия с Языковых курсов и Бесплатного образования</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>КЛЮЧ 2026</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Отработан БЕЗ ДАТЫ В ТЕКСТЕ</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Год в теле статьи обрёк бы её на ежегодную переделку. Год стоит в дате публикации и в datePublished</t>
         </is>
@@ -1235,7 +1252,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Сначала инфографика стояла на 25,0 % — в первый раздел добавлен абзац о том, что смотреть надо страницу своей программы, а не сводные статьи. После этого история уехала на 42,5 %, и её перенесли внутри раздела выше, перед заметкой про гранты. Стало 27,6 % и 38,2 %</t>
+          <t>Сначала инфографика стояла на 25,0 % — в первый раздел добавлен абзац о том, что смотреть надо страницу своей программы, а не сводные статьи. После этого история уехала на 42,5 %, и её перенесли внутри раздела выше, перед заметкой про гранты. Стало 28,0 % и 38,5 %</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2088,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>38 424 знака</t>
+          <t>38 519 знаков</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2112,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Инфографика 27,6 %, «Из личного опыта» 38,2 %, FAQ 66,3 %</t>
+          <t>Инфографика 28,0 %, «Из личного опыта» 38,5 %, FAQ 66,5 %</t>
         </is>
       </c>
     </row>

--- a/content/tz-obuchenie-v-kitae-dlya-russkih.xlsx
+++ b/content/tz-obuchenie-v-kitae-dlya-russkih.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Высшее образование в Китае для русских: четыре входа в вуз и что каждый стоит</t>
+          <t>Обучение в Китае для русских: четыре входа в вуз и что каждый стоит</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Высшее образование в Китае для русских начинается не с документов, а с выбора входа. Их четыре, и какой ваш — зависит от того, что уже есть на руках: аттестат с ЕГЭ, аттестат без ЕГЭ, диплом колледжа или диплом бакалавра. От входа зависят срок, язык обучения и цена. Разбираем все четыре, показываем, из чего складывается стоимость обучения в Китае, и честно говорим, что бывает с дипломом после выпуска.</t>
+          <t>Обучение в Китае для русских начинается не с документов, а с выбора входа. Их четыре, и какой ваш — зависит от того, что уже есть на руках: аттестат с ЕГЭ, аттестат без ЕГЭ, диплом колледжа или диплом бакалавра. От входа зависят срок, язык обучения и цена. Разбираем все четыре, показываем, из чего складывается стоимость, и честно говорим, что бывает с дипломом после выпуска.</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>38 519 знаков (лимит ≈ 50 000)</t>
+          <t>38 622 знака с адресами картинок Tilda (лимит ≈ 50 000)</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>28,0 % (норма 26–31 %)</t>
+          <t>27,6 % (норма 26–31 %)</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>38,5 %; FAQ на 66,5 %</t>
+          <t>38,2 %; FAQ на 66,3 %</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Общий вход (3): обучение в китае для русских, учиться в китае, образование в китае для русских — паспорт, раздел 1, адрес страницы. Вузы (5): высшее образование в китае, высшее образование в китае для россиян, китай вузы для русских, китай обучение в вузах для русских, обучение в университете китая для русских — ТАЙТЛ, H1, ПАСПОРТ, раздел 1 и таблица четырёх входов. Цена (3): стоимость, цена, 2026 — раздел 2, честно через структуру расходов</t>
+          <t>Общий вход (3): обучение в китае для русских, учиться в китае, образование в китае для русских — тайтл, H1, паспорт, раздел 1, адрес страницы. Вузы (5): высшее образование в китае, высшее образование в китае для россиян, китай вузы для русских, китай обучение в вузах для русских, обучение в университете китая для русских — раздел 1, таблица четырёх входов и FAQ. Цена (3): стоимость, цена, 2026 — раздел 2, честно через структуру расходов</t>
         </is>
       </c>
     </row>
@@ -939,17 +939,17 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>ТАЙТЛ ПЕРЕПИСАН ВТОРОЙ РАЗ, уже после сдачи</t>
+          <t>ИСТОРИЯ С ДВОЯКИМ ЧТЕНИЕМ — ЗАКРЫТА</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Было «Обучение в Китае для русских…», стало «Высшее образование в Китае для русских…»</t>
+          <t>Действует первый вариант: «Обучение в Китае для русских: четыре входа в вуз и что каждый стоит»</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Заказчик прочитала начало как «обучение китайцам» — будто мы учим китайцев. В файлах такого текста не было: слово «китайц» — 0 вхождений в статье, блоке T123 и ТЗ. Но если фраза читается двояко у заказчика, она прочитается двояко и у части читателей. «Высшее образование в Китае» — тоже ключ из брифа, и спутать его не с чем. Ключ «обучение в Китае для русских» остался в теле статьи и в адресе страницы</t>
+          <t>Заказчик прочитала начало как «обучение китайцам». Проверка по файлам: слово «китайц» — 0 вхождений в статье, блоке T123 и ТЗ, такого текста нигде не было. Предложено три замены, по просьбе заказчика поставлено «Высшее образование в Китае…». ЗАКАЗЧИК ОСТАВИЛА ПЕРВЫЙ ВАРИАНТ — он и действует. Записано, чтобы не возвращаться к вопросу заново</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Сначала инфографика стояла на 25,0 % — в первый раздел добавлен абзац о том, что смотреть надо страницу своей программы, а не сводные статьи. После этого история уехала на 42,5 %, и её перенесли внутри раздела выше, перед заметкой про гранты. Стало 28,0 % и 38,5 %</t>
+          <t>Сначала инфографика стояла на 25,0 % — в первый раздел добавлен абзац о том, что смотреть надо страницу своей программы, а не сводные статьи. После этого история уехала на 42,5 %, и её перенесли внутри раздела выше, перед заметкой про гранты. Стало 27,6 % и 38,2 %</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>38 519 знаков</t>
+          <t>38 622 знака (с адресами картинок Tilda)</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Инфографика 28,0 %, «Из личного опыта» 38,5 %, FAQ 66,5 %</t>
+          <t>Инфографика 27,6 %, «Из личного опыта» 38,2 %, FAQ 66,3 %</t>
         </is>
       </c>
     </row>
